--- a/data/trans_orig/RUIDO_1_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1_R-Edad-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19129</t>
+          <t>18800</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26191</t>
+          <t>26422</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>15064</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21273</t>
+          <t>21320</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36454</t>
+          <t>36296</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46052</t>
+          <t>45955</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10818</t>
+          <t>11147</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11378</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19700</t>
+          <t>19858</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51822</t>
+          <t>52929</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63460</t>
+          <t>63537</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70943</t>
+          <t>71422</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85395</t>
+          <t>84680</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>128640</t>
+          <t>128719</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>145278</t>
+          <t>146148</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11114</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22752</t>
+          <t>21645</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>13165</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26902</t>
+          <t>26423</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27141</t>
+          <t>26271</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43779</t>
+          <t>43700</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51086</t>
+          <t>51165</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66433</t>
+          <t>65875</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73704</t>
+          <t>73724</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93590</t>
+          <t>92579</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>129297</t>
+          <t>129167</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>154583</t>
+          <t>153899</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17887</t>
+          <t>18445</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>33155</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24291</t>
+          <t>25302</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44177</t>
+          <t>44157</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47617</t>
+          <t>48301</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72903</t>
+          <t>73033</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105041</t>
+          <t>105683</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>129077</t>
+          <t>128615</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93182</t>
+          <t>93350</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116913</t>
+          <t>116188</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>206356</t>
+          <t>205871</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242442</t>
+          <t>243707</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,94%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13625</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37661</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27303</t>
+          <t>28028</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51034</t>
+          <t>50866</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44476</t>
+          <t>43211</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80562</t>
+          <t>81047</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>240776</t>
+          <t>242664</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>274374</t>
+          <t>275054</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>268712</t>
+          <t>268513</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>303539</t>
+          <t>303444</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>523082</t>
+          <t>519201</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>570088</t>
+          <t>569331</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,33%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57169</t>
+          <t>56489</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90767</t>
+          <t>88879</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>82610</t>
+          <t>82705</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117437</t>
+          <t>117636</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>147603</t>
+          <t>148360</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>194609</t>
+          <t>198490</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_1_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1_R-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14438</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11520</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17031</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>68,9%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>54,97%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>81,27%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>23177</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>18800</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>26422</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>77,39%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>62,78%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>88,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15064</t>
+          <t>17421</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21320</t>
+          <t>23783</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>41597</t>
+          <t>35323</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36296</t>
+          <t>30780</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45955</t>
+          <t>39067</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,32%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6518</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3925</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9436</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>31,1%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18,73%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>45,03%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6770</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3525</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11147</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>22,61%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>11,77%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>37,22%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>9664</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14557</t>
+          <t>12718</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>8974</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19858</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20956</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20956</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20956</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>29947</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>29947</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29947</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26208</t>
+          <t>27085</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26208</t>
+          <t>27085</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26208</t>
+          <t>27085</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>56154</t>
+          <t>48041</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56154</t>
+          <t>48041</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56154</t>
+          <t>48041</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>68480</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>61933</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>73135</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>81,15%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>73,39%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>86,66%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>58355</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>52929</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>63537</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>78,25%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>70,97%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>85,2%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>78805</t>
+          <t>51860</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71422</t>
+          <t>46224</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84680</t>
+          <t>56619</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>137160</t>
+          <t>120340</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>128719</t>
+          <t>112263</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146148</t>
+          <t>127690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>83,96%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15910</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11255</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>22457</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>18,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>13,34%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>26,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>16219</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11037</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>21645</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>21,75%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>29,03%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19040</t>
+          <t>15840</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13165</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26423</t>
+          <t>21476</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>35259</t>
+          <t>31749</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>24399</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43700</t>
+          <t>39826</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>84390</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>84390</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>84390</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>74574</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>74574</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>74574</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>97845</t>
+          <t>67700</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>97845</t>
+          <t>67700</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>97845</t>
+          <t>67700</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>172419</t>
+          <t>152089</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>172419</t>
+          <t>152089</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>172419</t>
+          <t>152089</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>80884</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>70526</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>90053</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>71,5%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>62,34%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>79,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>59226</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>51165</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>65875</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>70,24%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>60,68%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>78,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>83954</t>
+          <t>58527</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73724</t>
+          <t>51209</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92579</t>
+          <t>65202</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>143179</t>
+          <t>139411</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>129167</t>
+          <t>128306</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>153899</t>
+          <t>151191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,61%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>32248</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>23079</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>42606</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>28,5%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>37,66%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>25094</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18445</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>33155</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>29,76%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>21,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>39,32%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33927</t>
+          <t>25686</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25302</t>
+          <t>19011</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44157</t>
+          <t>33004</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>59021</t>
+          <t>57935</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48301</t>
+          <t>46155</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73033</t>
+          <t>69040</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>34,98%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>113132</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>113132</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>113132</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>84320</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>84320</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>84320</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>117881</t>
+          <t>84213</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>117881</t>
+          <t>84213</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>117881</t>
+          <t>84213</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>202200</t>
+          <t>197346</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>202200</t>
+          <t>197346</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>202200</t>
+          <t>197346</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>115919</t>
+          <t>102809</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105683</t>
+          <t>89979</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128615</t>
+          <t>112170</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>107115</t>
+          <t>93409</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93350</t>
+          <t>85519</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116188</t>
+          <t>100912</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>223034</t>
+          <t>196218</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>205871</t>
+          <t>181592</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>243707</t>
+          <t>208055</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>36677</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27316</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>49507</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>26,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>35,49%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>26783</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14087</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>37019</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>25,94%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>37101</t>
+          <t>28362</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28028</t>
+          <t>20859</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50866</t>
+          <t>36252</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>63884</t>
+          <t>65039</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43211</t>
+          <t>53202</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>81047</t>
+          <t>79665</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>139486</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>139486</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>139486</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>142702</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>142702</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>142702</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>144216</t>
+          <t>121771</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>144216</t>
+          <t>121771</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>144216</t>
+          <t>121771</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>286918</t>
+          <t>261257</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>286918</t>
+          <t>261257</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>286918</t>
+          <t>261257</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>266611</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>249873</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>282316</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>74,48%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>69,8%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>78,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>351</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>256677</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>242664</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>275054</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>77,42%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>73,19%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>82,96%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>288294</t>
+          <t>224681</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>268513</t>
+          <t>211785</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>303444</t>
+          <t>236506</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>544970</t>
+          <t>491292</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>519201</t>
+          <t>469918</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>569331</t>
+          <t>509658</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>77,37%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>91354</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>75649</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>108092</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>25,52%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>21,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>30,2%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>74866</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>56489</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>88879</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>17,04%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>26,81%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>97855</t>
+          <t>76088</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>82705</t>
+          <t>64263</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117636</t>
+          <t>88984</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>172721</t>
+          <t>167441</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>148360</t>
+          <t>149075</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198490</t>
+          <t>188815</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>468</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
